--- a/ET-release8.1/Unity/Assets/Config/Excel/MapConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/MapConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>#</t>
   </si>
@@ -25,9 +25,6 @@
     <t>Type</t>
   </si>
   <si>
-    <t>测试说明</t>
-  </si>
-  <si>
     <t>名字</t>
   </si>
   <si>
@@ -71,19 +68,75 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>普隆德拉1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>普隆德拉2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Map1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Map2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>野外</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>普隆德拉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大人数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxPlayer</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否自动创建</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AutoCreate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否分线</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Div</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ValidTime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>地图脚本</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CmdList</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>有效时间（秒）</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -456,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:H7"/>
+  <dimension ref="C1:M7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -464,25 +517,27 @@
     <col min="3" max="3" width="12.625" style="2" customWidth="1"/>
     <col min="4" max="4" width="18.5" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
-    <col min="6" max="7" width="9.625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="28.75" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="6" max="8" width="9.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="10.5" style="2" customWidth="1"/>
+    <col min="13" max="13" width="28.75" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:13" x14ac:dyDescent="0.3">
       <c r="D1" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="2" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:13" x14ac:dyDescent="0.3">
       <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -490,19 +545,34 @@
         <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>5</v>
-      </c>
     </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -511,66 +581,122 @@
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C5" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>8</v>
+        <v>22</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
-        <v>11001</v>
+        <v>10001</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>18</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H6" s="1">
+        <v>50</v>
+      </c>
+      <c r="I6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1"/>
     </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
-        <v>11002</v>
+        <v>10002</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="H7" s="1">
+        <v>50</v>
+      </c>
+      <c r="I7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/MapConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/MapConfig.xlsx
@@ -694,7 +694,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L7" s="1"/>
     </row>

--- a/ET-release8.1/Unity/Assets/Config/Excel/MapConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/MapConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
   <si>
     <t>#</t>
   </si>
@@ -137,6 +137,26 @@
   </si>
   <si>
     <t>有效时间（秒）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始点</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartPoint</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>float[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.32,0,2.7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.5,0,-22</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -509,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:M7"/>
+  <dimension ref="C1:N7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -519,25 +539,25 @@
     <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
     <col min="6" max="8" width="9.625" style="2" customWidth="1"/>
     <col min="9" max="9" width="10.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="10.5" style="2" customWidth="1"/>
-    <col min="13" max="13" width="28.75" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="10" max="13" width="10.5" style="2" customWidth="1"/>
+    <col min="14" max="14" width="28.75" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -566,13 +586,16 @@
         <v>32</v>
       </c>
       <c r="L3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -599,13 +622,16 @@
         <v>28</v>
       </c>
       <c r="L4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
@@ -632,13 +658,16 @@
         <v>22</v>
       </c>
       <c r="L5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>10001</v>
       </c>
@@ -666,9 +695,12 @@
       <c r="K6" s="1">
         <v>0</v>
       </c>
-      <c r="L6" s="1"/>
+      <c r="L6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>10002</v>
       </c>
@@ -694,9 +726,12 @@
         <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>10</v>
-      </c>
-      <c r="L7" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/MapConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/MapConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
   <si>
     <t>#</t>
   </si>
@@ -157,6 +157,18 @@
   </si>
   <si>
     <t>13.5,0,-22</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>地图类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0安全区 1只能打野怪 2自由攻击</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -529,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:N7"/>
+  <dimension ref="C1:O7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -537,27 +549,32 @@
     <col min="3" max="3" width="12.625" style="2" customWidth="1"/>
     <col min="4" max="4" width="18.5" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
-    <col min="6" max="8" width="9.625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="10.5" style="2" customWidth="1"/>
-    <col min="14" max="14" width="28.75" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="6" max="7" width="9.625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="18" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="10.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="10.5" style="2" customWidth="1"/>
+    <col min="15" max="15" width="28.75" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D1" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="H1" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:15" x14ac:dyDescent="0.3">
       <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -574,28 +591,31 @@
         <v>12</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -610,28 +630,31 @@
         <v>13</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
@@ -649,25 +672,28 @@
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="K5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="O5" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>10001</v>
       </c>
@@ -684,23 +710,26 @@
         <v>15</v>
       </c>
       <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
         <v>50</v>
       </c>
-      <c r="I6" s="1" t="b">
-        <v>1</v>
-      </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
         <v>0</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="M6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
     </row>
-    <row r="7" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>10002</v>
       </c>
@@ -717,21 +746,24 @@
         <v>16</v>
       </c>
       <c r="H7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1">
         <v>50</v>
       </c>
-      <c r="I7" s="1" t="b">
-        <v>1</v>
-      </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="K7" s="1">
+      <c r="K7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
         <v>0</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
